--- a/InputData/io-model/ACTR/Avg Corp Tax Rate.xlsx
+++ b/InputData/io-model/ACTR/Avg Corp Tax Rate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Dropbox (Energy Innovation)\My Documents\Energy Policy Solutions\US\Models\eps-us\InputData\io-model\ACTR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mary Francis Swint\Vensim\eps-indonesia\InputData\io-model\ACTR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6361653D-74BA-485C-9BF1-04243361AEC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CDE3467-816E-4942-BE5F-D3062EB930FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8520" yWindow="2835" windowWidth="19200" windowHeight="11205" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -429,14 +429,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -444,32 +444,32 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B4" s="2">
         <v>2023</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -485,109 +485,113 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AE2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AF2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="45" customWidth="1"/>
-    <col min="2" max="2" width="26.21875" customWidth="1"/>
+    <col min="2" max="2" width="21.36328125" customWidth="1"/>
+    <col min="3" max="3" width="26.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B1">
+        <v>2020</v>
+      </c>
+      <c r="C1">
         <v>2021</v>
       </c>
-      <c r="C1">
+      <c r="D1">
         <v>2022</v>
       </c>
-      <c r="D1">
+      <c r="E1">
         <v>2023</v>
       </c>
-      <c r="E1">
+      <c r="F1">
         <v>2024</v>
       </c>
-      <c r="F1">
+      <c r="G1">
         <v>2025</v>
       </c>
-      <c r="G1">
+      <c r="H1">
         <v>2026</v>
       </c>
-      <c r="H1">
+      <c r="I1">
         <v>2027</v>
       </c>
-      <c r="I1">
+      <c r="J1">
         <v>2028</v>
       </c>
-      <c r="J1">
+      <c r="K1">
         <v>2029</v>
       </c>
-      <c r="K1">
+      <c r="L1">
         <v>2030</v>
       </c>
-      <c r="L1">
+      <c r="M1">
         <v>2031</v>
       </c>
-      <c r="M1">
+      <c r="N1">
         <v>2032</v>
       </c>
-      <c r="N1">
+      <c r="O1">
         <v>2033</v>
       </c>
-      <c r="O1">
+      <c r="P1">
         <v>2034</v>
       </c>
-      <c r="P1">
+      <c r="Q1">
         <v>2035</v>
       </c>
-      <c r="Q1">
+      <c r="R1">
         <v>2036</v>
       </c>
-      <c r="R1">
+      <c r="S1">
         <v>2037</v>
       </c>
-      <c r="S1">
+      <c r="T1">
         <v>2038</v>
       </c>
-      <c r="T1">
+      <c r="U1">
         <v>2039</v>
       </c>
-      <c r="U1">
+      <c r="V1">
         <v>2040</v>
       </c>
-      <c r="V1">
+      <c r="W1">
         <v>2041</v>
       </c>
-      <c r="W1">
+      <c r="X1">
         <v>2042</v>
       </c>
-      <c r="X1">
+      <c r="Y1">
         <v>2043</v>
       </c>
-      <c r="Y1">
+      <c r="Z1">
         <v>2044</v>
       </c>
-      <c r="Z1">
+      <c r="AA1">
         <v>2045</v>
       </c>
-      <c r="AA1">
+      <c r="AB1">
         <v>2046</v>
       </c>
-      <c r="AB1">
+      <c r="AC1">
         <v>2047</v>
       </c>
-      <c r="AC1">
+      <c r="AD1">
         <v>2048</v>
       </c>
-      <c r="AD1">
+      <c r="AE1">
         <v>2049</v>
       </c>
-      <c r="AE1">
+      <c r="AF1">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -595,19 +599,18 @@
         <v>0.26</v>
       </c>
       <c r="C2">
-        <f>$B$2</f>
         <v>0.26</v>
       </c>
       <c r="D2">
-        <f>$B$2</f>
+        <f>$C$2</f>
         <v>0.26</v>
       </c>
       <c r="E2">
-        <f t="shared" ref="E2:O2" si="0">$B$2</f>
+        <f>$C$2</f>
         <v>0.26</v>
       </c>
       <c r="F2">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="F2:P2" si="0">$C$2</f>
         <v>0.26</v>
       </c>
       <c r="G2">
@@ -647,19 +650,19 @@
         <v>0.26</v>
       </c>
       <c r="P2">
-        <f>$B$2</f>
+        <f t="shared" si="0"/>
         <v>0.26</v>
       </c>
       <c r="Q2">
-        <f>$B$2</f>
+        <f>$C$2</f>
         <v>0.26</v>
       </c>
       <c r="R2">
-        <f t="shared" ref="R2:V2" si="1">$B$2</f>
+        <f>$C$2</f>
         <v>0.26</v>
       </c>
       <c r="S2">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="S2:W2" si="1">$C$2</f>
         <v>0.26</v>
       </c>
       <c r="T2">
@@ -675,19 +678,19 @@
         <v>0.26</v>
       </c>
       <c r="W2">
-        <f>$B$2</f>
+        <f t="shared" si="1"/>
         <v>0.26</v>
       </c>
       <c r="X2">
-        <f>$B$2</f>
+        <f>$C$2</f>
         <v>0.26</v>
       </c>
       <c r="Y2">
-        <f t="shared" ref="Y2:AA2" si="2">$B$2</f>
+        <f>$C$2</f>
         <v>0.26</v>
       </c>
       <c r="Z2">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="Z2:AB2" si="2">$C$2</f>
         <v>0.26</v>
       </c>
       <c r="AA2">
@@ -695,18 +698,22 @@
         <v>0.26</v>
       </c>
       <c r="AB2">
-        <f>$B$2</f>
+        <f t="shared" si="2"/>
         <v>0.26</v>
       </c>
       <c r="AC2">
-        <f>$B$2</f>
+        <f>$C$2</f>
         <v>0.26</v>
       </c>
       <c r="AD2">
-        <f t="shared" ref="AD2:AM2" si="3">$B$2</f>
+        <f>$C$2</f>
         <v>0.26</v>
       </c>
       <c r="AE2">
+        <f t="shared" ref="AE2:AF2" si="3">$C$2</f>
+        <v>0.26</v>
+      </c>
+      <c r="AF2">
         <f t="shared" si="3"/>
         <v>0.26</v>
       </c>

--- a/InputData/io-model/ACTR/Avg Corp Tax Rate.xlsx
+++ b/InputData/io-model/ACTR/Avg Corp Tax Rate.xlsx
@@ -1,23 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28816"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mary Francis Swint\Vensim\eps-indonesia\InputData\io-model\ACTR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Dropbox (Energy Innovation)\My Documents\Energy Policy Solutions\US\Models\eps-us\InputData\io-model\ACTR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CDE3467-816E-4942-BE5F-D3062EB930FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{6361653D-74BA-485C-9BF1-04243361AEC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D0DB322-800A-460D-8A43-D583823012CB}"/>
   <bookViews>
-    <workbookView xWindow="8520" yWindow="2835" windowWidth="19200" windowHeight="11205" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="ACTR" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -34,27 +37,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+  <si>
+    <t>ACTR Average Corporate Tax Rate</t>
+  </si>
   <si>
     <t>Source:</t>
   </si>
   <si>
-    <t>Notes:</t>
+    <t>PwC</t>
   </si>
   <si>
-    <t>ACTR Average Corporate Tax Rate</t>
+    <t>Indoneisia - Taxes on corporate income</t>
   </si>
   <si>
-    <t>Peter Peterson Foundation</t>
+    <t>https://taxsummaries.pwc.com/indonesia/corporate/taxes-on-corporate-income</t>
   </si>
   <si>
-    <t>The US Corporate Tax System Explained</t>
-  </si>
-  <si>
-    <t>https://www.pgpf.org/budget-basics/the-us-corporate-tax-system-explained</t>
-  </si>
-  <si>
-    <t>Combined federal and state corporate tax rate</t>
+    <t>Notes:</t>
   </si>
   <si>
     <t>This is the average corporate tax rate paid, including national and subnational rates</t>
@@ -70,7 +70,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -429,54 +429,52 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="4" spans="1:2" ht="15">
+      <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B4" s="2">
-        <v>2023</v>
+    <row r="5" spans="1:2">
+      <c r="B5">
+        <v>2024</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B5" t="s">
+    <row r="6" spans="1:2" ht="15">
+      <c r="B6" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B6" s="3" t="s">
+    <row r="9" spans="1:2">
+      <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B7" t="s">
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B6" r:id="rId1" xr:uid="{73CC3535-2E49-49DD-A2B5-025E4A45DFF8}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -485,240 +483,404 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AF2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AE2"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="45" customWidth="1"/>
-    <col min="2" max="2" width="21.36328125" customWidth="1"/>
-    <col min="3" max="3" width="26.1796875" customWidth="1"/>
+    <col min="2" max="2" width="26.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31">
       <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1">
+        <v>2021</v>
+      </c>
+      <c r="C1">
+        <v>2022</v>
+      </c>
+      <c r="D1">
+        <v>2023</v>
+      </c>
+      <c r="E1">
+        <v>2024</v>
+      </c>
+      <c r="F1">
+        <v>2025</v>
+      </c>
+      <c r="G1">
+        <v>2026</v>
+      </c>
+      <c r="H1">
+        <v>2027</v>
+      </c>
+      <c r="I1">
+        <v>2028</v>
+      </c>
+      <c r="J1">
+        <v>2029</v>
+      </c>
+      <c r="K1">
+        <v>2030</v>
+      </c>
+      <c r="L1">
+        <v>2031</v>
+      </c>
+      <c r="M1">
+        <v>2032</v>
+      </c>
+      <c r="N1">
+        <v>2033</v>
+      </c>
+      <c r="O1">
+        <v>2034</v>
+      </c>
+      <c r="P1">
+        <v>2035</v>
+      </c>
+      <c r="Q1">
+        <v>2036</v>
+      </c>
+      <c r="R1">
+        <v>2037</v>
+      </c>
+      <c r="S1">
+        <v>2038</v>
+      </c>
+      <c r="T1">
+        <v>2039</v>
+      </c>
+      <c r="U1">
+        <v>2040</v>
+      </c>
+      <c r="V1">
+        <v>2041</v>
+      </c>
+      <c r="W1">
+        <v>2042</v>
+      </c>
+      <c r="X1">
+        <v>2043</v>
+      </c>
+      <c r="Y1">
+        <v>2044</v>
+      </c>
+      <c r="Z1">
+        <v>2045</v>
+      </c>
+      <c r="AA1">
+        <v>2046</v>
+      </c>
+      <c r="AB1">
+        <v>2047</v>
+      </c>
+      <c r="AC1">
+        <v>2048</v>
+      </c>
+      <c r="AD1">
+        <v>2049</v>
+      </c>
+      <c r="AE1">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31">
+      <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="B1">
-        <v>2020</v>
-      </c>
-      <c r="C1">
-        <v>2021</v>
-      </c>
-      <c r="D1">
-        <v>2022</v>
-      </c>
-      <c r="E1">
-        <v>2023</v>
-      </c>
-      <c r="F1">
-        <v>2024</v>
-      </c>
-      <c r="G1">
-        <v>2025</v>
-      </c>
-      <c r="H1">
-        <v>2026</v>
-      </c>
-      <c r="I1">
-        <v>2027</v>
-      </c>
-      <c r="J1">
-        <v>2028</v>
-      </c>
-      <c r="K1">
-        <v>2029</v>
-      </c>
-      <c r="L1">
-        <v>2030</v>
-      </c>
-      <c r="M1">
-        <v>2031</v>
-      </c>
-      <c r="N1">
-        <v>2032</v>
-      </c>
-      <c r="O1">
-        <v>2033</v>
-      </c>
-      <c r="P1">
-        <v>2034</v>
-      </c>
-      <c r="Q1">
-        <v>2035</v>
-      </c>
-      <c r="R1">
-        <v>2036</v>
-      </c>
-      <c r="S1">
-        <v>2037</v>
-      </c>
-      <c r="T1">
-        <v>2038</v>
-      </c>
-      <c r="U1">
-        <v>2039</v>
-      </c>
-      <c r="V1">
-        <v>2040</v>
-      </c>
-      <c r="W1">
-        <v>2041</v>
-      </c>
-      <c r="X1">
-        <v>2042</v>
-      </c>
-      <c r="Y1">
-        <v>2043</v>
-      </c>
-      <c r="Z1">
-        <v>2044</v>
-      </c>
-      <c r="AA1">
-        <v>2045</v>
-      </c>
-      <c r="AB1">
-        <v>2046</v>
-      </c>
-      <c r="AC1">
-        <v>2047</v>
-      </c>
-      <c r="AD1">
-        <v>2048</v>
-      </c>
-      <c r="AE1">
-        <v>2049</v>
-      </c>
-      <c r="AF1">
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
       <c r="B2">
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="C2">
-        <v>0.26</v>
+        <f>$B$2</f>
+        <v>0.22</v>
       </c>
       <c r="D2">
-        <f>$C$2</f>
-        <v>0.26</v>
+        <f>$B$2</f>
+        <v>0.22</v>
       </c>
       <c r="E2">
-        <f>$C$2</f>
-        <v>0.26</v>
+        <f t="shared" ref="E2:O2" si="0">$B$2</f>
+        <v>0.22</v>
       </c>
       <c r="F2">
-        <f t="shared" ref="F2:P2" si="0">$C$2</f>
-        <v>0.26</v>
+        <f t="shared" si="0"/>
+        <v>0.22</v>
       </c>
       <c r="G2">
         <f t="shared" si="0"/>
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="H2">
         <f t="shared" si="0"/>
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="I2">
         <f t="shared" si="0"/>
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="J2">
         <f t="shared" si="0"/>
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="K2">
         <f t="shared" si="0"/>
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="L2">
         <f t="shared" si="0"/>
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="M2">
         <f t="shared" si="0"/>
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="N2">
         <f t="shared" si="0"/>
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="O2">
         <f t="shared" si="0"/>
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="P2">
-        <f t="shared" si="0"/>
-        <v>0.26</v>
+        <f>$B$2</f>
+        <v>0.22</v>
       </c>
       <c r="Q2">
-        <f>$C$2</f>
-        <v>0.26</v>
+        <f>$B$2</f>
+        <v>0.22</v>
       </c>
       <c r="R2">
-        <f>$C$2</f>
-        <v>0.26</v>
+        <f t="shared" ref="R2:V2" si="1">$B$2</f>
+        <v>0.22</v>
       </c>
       <c r="S2">
-        <f t="shared" ref="S2:W2" si="1">$C$2</f>
-        <v>0.26</v>
+        <f t="shared" si="1"/>
+        <v>0.22</v>
       </c>
       <c r="T2">
         <f t="shared" si="1"/>
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="U2">
         <f t="shared" si="1"/>
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="V2">
         <f t="shared" si="1"/>
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="W2">
-        <f t="shared" si="1"/>
-        <v>0.26</v>
+        <f>$B$2</f>
+        <v>0.22</v>
       </c>
       <c r="X2">
-        <f>$C$2</f>
-        <v>0.26</v>
+        <f>$B$2</f>
+        <v>0.22</v>
       </c>
       <c r="Y2">
-        <f>$C$2</f>
-        <v>0.26</v>
+        <f t="shared" ref="Y2:AA2" si="2">$B$2</f>
+        <v>0.22</v>
       </c>
       <c r="Z2">
-        <f t="shared" ref="Z2:AB2" si="2">$C$2</f>
-        <v>0.26</v>
+        <f t="shared" si="2"/>
+        <v>0.22</v>
       </c>
       <c r="AA2">
         <f t="shared" si="2"/>
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="AB2">
-        <f t="shared" si="2"/>
-        <v>0.26</v>
+        <f>$B$2</f>
+        <v>0.22</v>
       </c>
       <c r="AC2">
-        <f>$C$2</f>
-        <v>0.26</v>
+        <f>$B$2</f>
+        <v>0.22</v>
       </c>
       <c r="AD2">
-        <f>$C$2</f>
-        <v>0.26</v>
+        <f t="shared" ref="AD2:AM2" si="3">$B$2</f>
+        <v>0.22</v>
       </c>
       <c r="AE2">
-        <f t="shared" ref="AE2:AF2" si="3">$C$2</f>
-        <v>0.26</v>
-      </c>
-      <c r="AF2">
         <f t="shared" si="3"/>
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002041A8AB53924247A2770D65450F5227" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="90fff4f083191fe75a03dbd50c7739fc">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1659011e-6b88-4225-9a61-aaf33aaf19e8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7fee88694a371868130ae0617c69143c" ns2:_="">
+    <xsd:import namespace="1659011e-6b88-4225-9a61-aaf33aaf19e8"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="1659011e-6b88-4225-9a61-aaf33aaf19e8" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{842CB702-5037-4BB6-B925-4AE7E56A606B}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7070F1A8-AF40-4F64-8B04-0E93C1A46B51}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A77B510-8BB3-440F-9D15-960370F2E3EC}"/>
 </file>
--- a/InputData/io-model/ACTR/Avg Corp Tax Rate.xlsx
+++ b/InputData/io-model/ACTR/Avg Corp Tax Rate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28816"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Dropbox (Energy Innovation)\My Documents\Energy Policy Solutions\US\Models\eps-us\InputData\io-model\ACTR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel Goldstein\Desktop\EPS Models\Indonesia EPS\InputData\io-model\ACTR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{6361653D-74BA-485C-9BF1-04243361AEC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D0DB322-800A-460D-8A43-D583823012CB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C9423F7-6946-4385-9E1F-2B7782A17999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38190" yWindow="1815" windowWidth="23235" windowHeight="13365" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -70,7 +70,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -116,13 +116,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -429,14 +430,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -444,27 +445,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>2024</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -483,129 +484,131 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AE2"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <dimension ref="A1:AF2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="45" customWidth="1"/>
-    <col min="2" max="2" width="26.28515625" customWidth="1"/>
+    <col min="1" max="2" width="45" customWidth="1"/>
+    <col min="3" max="3" width="26.33203125" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B1">
+      <c r="B1" s="4">
+        <v>2020</v>
+      </c>
+      <c r="C1" s="4">
         <v>2021</v>
       </c>
-      <c r="C1">
+      <c r="D1">
         <v>2022</v>
       </c>
-      <c r="D1">
+      <c r="E1">
         <v>2023</v>
       </c>
-      <c r="E1">
+      <c r="F1">
         <v>2024</v>
       </c>
-      <c r="F1">
+      <c r="G1">
         <v>2025</v>
       </c>
-      <c r="G1">
+      <c r="H1">
         <v>2026</v>
       </c>
-      <c r="H1">
+      <c r="I1">
         <v>2027</v>
       </c>
-      <c r="I1">
+      <c r="J1">
         <v>2028</v>
       </c>
-      <c r="J1">
+      <c r="K1">
         <v>2029</v>
       </c>
-      <c r="K1">
+      <c r="L1">
         <v>2030</v>
       </c>
-      <c r="L1">
+      <c r="M1">
         <v>2031</v>
       </c>
-      <c r="M1">
+      <c r="N1">
         <v>2032</v>
       </c>
-      <c r="N1">
+      <c r="O1">
         <v>2033</v>
       </c>
-      <c r="O1">
+      <c r="P1">
         <v>2034</v>
       </c>
-      <c r="P1">
+      <c r="Q1">
         <v>2035</v>
       </c>
-      <c r="Q1">
+      <c r="R1">
         <v>2036</v>
       </c>
-      <c r="R1">
+      <c r="S1">
         <v>2037</v>
       </c>
-      <c r="S1">
+      <c r="T1">
         <v>2038</v>
       </c>
-      <c r="T1">
+      <c r="U1">
         <v>2039</v>
       </c>
-      <c r="U1">
+      <c r="V1">
         <v>2040</v>
       </c>
-      <c r="V1">
+      <c r="W1">
         <v>2041</v>
       </c>
-      <c r="W1">
+      <c r="X1">
         <v>2042</v>
       </c>
-      <c r="X1">
+      <c r="Y1">
         <v>2043</v>
       </c>
-      <c r="Y1">
+      <c r="Z1">
         <v>2044</v>
       </c>
-      <c r="Z1">
+      <c r="AA1">
         <v>2045</v>
       </c>
-      <c r="AA1">
+      <c r="AB1">
         <v>2046</v>
       </c>
-      <c r="AB1">
+      <c r="AC1">
         <v>2047</v>
       </c>
-      <c r="AC1">
+      <c r="AD1">
         <v>2048</v>
       </c>
-      <c r="AD1">
+      <c r="AE1">
         <v>2049</v>
       </c>
-      <c r="AE1">
+      <c r="AF1">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="B2">
-        <v>0.22</v>
-      </c>
-      <c r="C2">
-        <f>$B$2</f>
+      <c r="B2" s="4">
+        <v>0.22</v>
+      </c>
+      <c r="C2" s="4">
         <v>0.22</v>
       </c>
       <c r="D2">
-        <f>$B$2</f>
+        <f>$C$2</f>
         <v>0.22</v>
       </c>
       <c r="E2">
-        <f t="shared" ref="E2:O2" si="0">$B$2</f>
+        <f>$C$2</f>
         <v>0.22</v>
       </c>
       <c r="F2">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="F2:P2" si="0">$C$2</f>
         <v>0.22</v>
       </c>
       <c r="G2">
@@ -645,19 +648,19 @@
         <v>0.22</v>
       </c>
       <c r="P2">
-        <f>$B$2</f>
+        <f t="shared" si="0"/>
         <v>0.22</v>
       </c>
       <c r="Q2">
-        <f>$B$2</f>
+        <f>$C$2</f>
         <v>0.22</v>
       </c>
       <c r="R2">
-        <f t="shared" ref="R2:V2" si="1">$B$2</f>
+        <f>$C$2</f>
         <v>0.22</v>
       </c>
       <c r="S2">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="S2:W2" si="1">$C$2</f>
         <v>0.22</v>
       </c>
       <c r="T2">
@@ -673,19 +676,19 @@
         <v>0.22</v>
       </c>
       <c r="W2">
-        <f>$B$2</f>
+        <f t="shared" si="1"/>
         <v>0.22</v>
       </c>
       <c r="X2">
-        <f>$B$2</f>
+        <f>$C$2</f>
         <v>0.22</v>
       </c>
       <c r="Y2">
-        <f t="shared" ref="Y2:AA2" si="2">$B$2</f>
+        <f>$C$2</f>
         <v>0.22</v>
       </c>
       <c r="Z2">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="Z2:AB2" si="2">$C$2</f>
         <v>0.22</v>
       </c>
       <c r="AA2">
@@ -693,18 +696,22 @@
         <v>0.22</v>
       </c>
       <c r="AB2">
-        <f>$B$2</f>
+        <f t="shared" si="2"/>
         <v>0.22</v>
       </c>
       <c r="AC2">
-        <f>$B$2</f>
+        <f>$C$2</f>
         <v>0.22</v>
       </c>
       <c r="AD2">
-        <f t="shared" ref="AD2:AM2" si="3">$B$2</f>
+        <f>$C$2</f>
         <v>0.22</v>
       </c>
       <c r="AE2">
+        <f t="shared" ref="AE2:AF2" si="3">$C$2</f>
+        <v>0.22</v>
+      </c>
+      <c r="AF2">
         <f t="shared" si="3"/>
         <v>0.22</v>
       </c>
@@ -715,21 +722,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002041A8AB53924247A2770D65450F5227" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="90fff4f083191fe75a03dbd50c7739fc">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1659011e-6b88-4225-9a61-aaf33aaf19e8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7fee88694a371868130ae0617c69143c" ns2:_="">
     <xsd:import namespace="1659011e-6b88-4225-9a61-aaf33aaf19e8"/>
@@ -873,14 +865,52 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{842CB702-5037-4BB6-B925-4AE7E56A606B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A77B510-8BB3-440F-9D15-960370F2E3EC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="1659011e-6b88-4225-9a61-aaf33aaf19e8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7070F1A8-AF40-4F64-8B04-0E93C1A46B51}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7070F1A8-AF40-4F64-8B04-0E93C1A46B51}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A77B510-8BB3-440F-9D15-960370F2E3EC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{842CB702-5037-4BB6-B925-4AE7E56A606B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>